--- a/tanoshimi/docs/04_ERD_테이블정의서.xlsx
+++ b/tanoshimi/docs/04_ERD_테이블정의서.xlsx
@@ -589,21 +589,21 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>■ 결제/예약 기능 제거 예정 (v16 확정, 미완료)</t>
+          <t xml:space="preserve">■ 결제/예약 기능 제거 완료 (v21)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reservations, reservation_payments, trip_schedule_payments 3개 테이블은</t>
+          <t xml:space="preserve">  reservations, reservation_payments, trip_schedule_payments 3개 테이블과</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  제거가 확정되었으나 아직 schema.sql·엔티티에 남아있다. 정의서에는 '제거 예정' 표기.</t>
+          <t xml:space="preserve">  trip_schedules.reservation_id 컬럼을 제거했다(feature/remove-reservation-payment). 기존 DB는 migration_v21 실행. 아래 정의서에는 '[v21 제거됨]' 표기.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>1:N → parties, reservations</t>
+          <t xml:space="preserve">1:N → parties</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>패키지 예약 [제거 예정]</t>
+          <t xml:space="preserve">패키지 예약 [v21 제거됨]</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 패키지 예약. 결제 기능 제거 결정에 따라 삭제 예정이나 아직 스키마·엔티티에 잔존.</t>
+          <t xml:space="preserve">[v21 제거됨] 패키지 예약. 결제 기능 제거로 schema.sql·엔티티·마이그레이션에서 삭제(migration_v21).</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>패키지 결제 [제거 예정]</t>
+          <t xml:space="preserve">패키지 결제 [v21 제거됨]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 패키지 대금 인원별 분할 결제.</t>
+          <t xml:space="preserve">[v21 제거됨] 패키지 대금 인원별 분할 결제. 결제 기능 제거로 삭제.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>액티비티 결제 [제거 예정]</t>
+          <t xml:space="preserve">액티비티 결제 [v21 제거됨]</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 액티비티 결제. 제출 시점에 인원별 생성.</t>
+          <t xml:space="preserve">[v21 제거됨] 액티비티 결제. 결제 기능 제거로 삭제.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>항공+숙박+교통 패키지(더미 고정가 데이터).  (주요 관계: 1:N → parties, reservations / 담당: 허수연)</t>
+          <t xml:space="preserve">항공+숙박+교통 패키지(더미 고정가 데이터).  (주요 관계: 1:N → parties / 담당: 허수연)</t>
         </is>
       </c>
       <c r="C76" s="12" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>패키지 예약 [제거 예정]</t>
+          <t xml:space="preserve">패키지 예약 [v21 제거됨]</t>
         </is>
       </c>
       <c r="H170" s="9" t="n"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 패키지 예약. 결제 기능 제거 결정에 따라 삭제 예정이나 아직 스키마·엔티티에 잔존.  (주요 관계: N:1 → parties, users, tours / 1:N → reservation_payments / 담당: 허수연)</t>
+          <t xml:space="preserve">[v21 제거됨] 패키지 예약. 결제 기능 제거로 schema.sql·엔티티에서 삭제(migration_v21). 아래는 참고용 정의.  (담당: 허수연)</t>
         </is>
       </c>
       <c r="C171" s="12" t="n"/>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>패키지 결제 [제거 예정]</t>
+          <t xml:space="preserve">패키지 결제 [v21 제거됨]</t>
         </is>
       </c>
       <c r="H186" s="9" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 패키지 대금 인원별 분할 결제.  (주요 관계: N:1 → reservations, users / 담당: 허수연)</t>
+          <t xml:space="preserve">[v21 제거됨] 패키지 대금 인원별 분할 결제. 결제 기능 제거로 삭제.  (담당: 허수연)</t>
         </is>
       </c>
       <c r="C187" s="12" t="n"/>
@@ -8540,7 +8540,7 @@
       <c r="J202" s="5" t="inlineStr"/>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>[제거 예정 연관]</t>
+          <t xml:space="preserve">[v21 제거됨] reservation_id 컬럼 삭제</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>액티비티 결제 [제거 예정]</t>
+          <t xml:space="preserve">액티비티 결제 [v21 제거됨]</t>
         </is>
       </c>
       <c r="H230" s="9" t="n"/>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>[v16 제거 확정, 미완료] 액티비티 결제. 제출 시점에 인원별 생성.  (주요 관계: N:1 → trip_schedules, users / 담당: 정태웅)</t>
+          <t xml:space="preserve">[v21 제거됨] 액티비티 결제. 결제 기능 제거로 삭제.  (담당: 정태웅)</t>
         </is>
       </c>
       <c r="C231" s="12" t="n"/>
@@ -12834,7 +12834,7 @@
       <c r="J336" s="5" t="inlineStr"/>
       <c r="K336" s="6" t="inlineStr">
         <is>
-          <t>trip_reminder, party_approved 등</t>
+          <t xml:space="preserve">party_approved, new_follower, new_comment 등 (trip_reminder는 v21에서 발행 주체 삭제)</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>여행 리마인더 알림</t>
+          <t xml:space="preserve">여행 리마인더 알림 (미사용 - 발행 주체 v21 삭제)</t>
         </is>
       </c>
       <c r="D417" s="6" t="inlineStr">
